--- a/supplementary/Supplementary_Dataset_S1_CCD.xlsx
+++ b/supplementary/Supplementary_Dataset_S1_CCD.xlsx
@@ -6012,7 +6012,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-08 20:33 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
+          <t>Generated 2026-09-16 07:05 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
         </is>
       </c>
     </row>

--- a/supplementary/Supplementary_Dataset_S1_CCD.xlsx
+++ b/supplementary/Supplementary_Dataset_S1_CCD.xlsx
@@ -6012,7 +6012,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16 07:05 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
+          <t>Generated 2026-09-16 07:07 by Paper/make_supplementary_datasets.py. Rerun that script after any change to the workflow so these numbers stay in step with the analysis.</t>
         </is>
       </c>
     </row>
